--- a/output/pdf_financials_xlsx/GG.xlsx
+++ b/output/pdf_financials_xlsx/GG.xlsx
@@ -3303,31 +3303,31 @@
         <v>0.00032</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8.341571999999999</v>
+        <v>6.531004</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.745871</v>
+        <v>17.015276</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.936392</v>
+        <v>12.175929</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.83753</v>
+        <v>11.491337</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.8594540000000001</v>
+        <v>2.746633</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.369988</v>
+        <v>2.193728</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.582958</v>
+        <v>4.133659</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.849945</v>
+        <v>6.022997</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.19652</v>
+        <v>4.398373</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>1.410503</v>
@@ -5657,46 +5657,46 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.587651</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.150905</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.345154</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.487961</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.814369</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.077781</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.280668</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.515382</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.626081</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.74427</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.829896</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.887763</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.639212</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.29096</v>
       </c>
     </row>
     <row r="93">
@@ -9773,7 +9773,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10631,7 +10635,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -11780,7 +11788,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -11948,7 +11960,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12626,7 +12638,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -13207,7 +13219,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -13642,7 +13658,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14544,7 +14564,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -15357,7 +15381,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GG.xlsx
+++ b/output/pdf_financials_xlsx/GG.xlsx
@@ -2572,37 +2572,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.531004</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>15.269405</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.239537</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>9.653807</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.887179</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.82374</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.550701</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.173052</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.201853</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.889561</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.639033</v>
@@ -2676,37 +2676,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.00032</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.531004</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>15.269405</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>11.239537</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>9.653807</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.887179</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.82374</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.550701</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.173052</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.201853</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.889561</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.639033</v>
@@ -3300,37 +3300,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.00032</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.531004</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>17.015276</v>
+        <v>1.745871</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.175929</v>
+        <v>0.936392</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.491337</v>
+        <v>1.83753</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.746633</v>
+        <v>0.8594540000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.193728</v>
+        <v>1.369988</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.133659</v>
+        <v>1.582958</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.022997</v>
+        <v>1.849945</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.398373</v>
+        <v>2.19652</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.410503</v>
+        <v>0.520942</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.962627</v>
@@ -10807,7 +10807,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
